--- a/LubanConfig/MiniTemplate/Datas/基础数据/#经济系统配置表.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/基础数据/#经济系统配置表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="64">
   <si>
     <t>每日商店</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -182,6 +182,98 @@
   </si>
   <si>
     <t>类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>钻石价格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>购买次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一个500，一个2000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这里决定了金币和钻石的兑换关系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算一下纯靠通关，不看广告的话，获得的资源最多能打到哪里</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得次数 = 广告获得次数 + 钻石购买次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>比例都是总需求-固定值的剩余的比例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>注意：平均每次开精致宝箱的收益要高于普通宝箱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宝箱产出要有一个最低值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2绿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2蓝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1紫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1广告位</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10次广告，每个广告获得500金币。 剩余的5000金币，分配给两个钻石购买的礼包： 1000金币  100钻石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工作1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工作2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金币每日固定数值，要加入购买次数的考虑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金币和钻石的价值分配，要考虑到  广告获得金币的占比</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工作3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>考虑每日商店的购买次数，以及每种碎片的钻石定价</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -189,7 +281,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -204,8 +296,17 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -215,6 +316,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -246,14 +359,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -534,44 +649,62 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:S35"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9" style="4"/>
-    <col min="2" max="2" width="14.875" style="4" customWidth="1"/>
-    <col min="3" max="6" width="9" style="4"/>
+    <col min="1" max="1" width="9" style="3"/>
+    <col min="2" max="2" width="14.875" style="3" customWidth="1"/>
+    <col min="3" max="6" width="9" style="3"/>
     <col min="13" max="13" width="23.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>21</v>
       </c>
@@ -589,7 +722,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>23</v>
       </c>
@@ -609,376 +742,478 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B5" s="4" t="s">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="B5" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="6">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C6" s="4" t="s">
+      <c r="M5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="C6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="3">
         <v>30</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C7" s="4" t="s">
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="M6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="C7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="3">
         <v>15</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C8" s="4" t="s">
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="M7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="C8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="3">
         <v>4</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B9" s="4" t="s">
+      <c r="H8">
         <v>2</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="M8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="B9" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="4">
+      <c r="D9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="3">
         <v>0.1</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="G9">
+        <v>25</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="I9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="C10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="B11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>200</v>
+      </c>
+      <c r="H11">
+        <v>8</v>
+      </c>
+      <c r="I11">
+        <v>9</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="C12" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="5">
+        <v>100</v>
+      </c>
+      <c r="I12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="C13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="C14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="S14" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="C15" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="B16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="6">
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <v>500</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="M16" t="s">
+        <v>44</v>
+      </c>
+      <c r="N16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="C17" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="5">
+        <v>10000</v>
+      </c>
+      <c r="M17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="5">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="C19" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="C20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="C21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="M21" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="C22" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="C23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B24" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="M24" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="C25" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="M25" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="4" t="s">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="C26" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="4">
+      <c r="D26" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="3">
         <v>0.1</v>
       </c>
-      <c r="M10" t="s">
+      <c r="M26" t="s">
         <v>28</v>
       </c>
-      <c r="N10">
+      <c r="N26">
         <f>SUMIFS(E:E, C:C, "*蓝色碎片*", D:D, "*比例*")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B11" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="4" t="s">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="C27" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="2">
+        <v>100</v>
+      </c>
+      <c r="M27" t="s">
+        <v>29</v>
+      </c>
+      <c r="N27">
+        <f>SUMIFS(E:E, C:C, "*绿色碎片*", D:D, "*比例*")</f>
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="C28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="4">
-        <v>1</v>
-      </c>
-      <c r="M11" t="s">
-        <v>29</v>
-      </c>
-      <c r="N11">
-        <f>SUMIFS(E:E, C:C, "*绿色碎片*", D:D, "*比例*")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C12" s="4" t="s">
+      <c r="E28" s="3">
         <v>10</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="4">
-        <v>1000</v>
-      </c>
-      <c r="M12" t="s">
+      <c r="M28" t="s">
         <v>30</v>
       </c>
-      <c r="N12">
+      <c r="N28">
         <f>SUMIFS(E:E, C:C, "*紫色碎片*", D:D, "*比例*")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C13" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="4">
-        <v>0.3</v>
-      </c>
-      <c r="M13" t="s">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B29" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="2">
+        <v>50</v>
+      </c>
+      <c r="M29" t="s">
         <v>31</v>
       </c>
-      <c r="N13">
+      <c r="N29">
         <f>SUMIFS(E:E, C:C, "*金币*", D:D, "*比例*")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="4">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C15" s="4" t="s">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B30" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="5">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="C31" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="C32" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="4">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B16" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C17" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="4">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B18" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" s="4">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C19" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="4">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C20" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E20" s="4">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C21" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" s="4">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C22" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22" s="4">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C23" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="4" t="s">
+      <c r="D32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E23" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B24" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E24" s="4">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C25" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E25" s="4">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C26" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E26" s="4">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C27" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C28" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E28" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B29" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="4">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B30" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C31" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="4">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C32" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="4">
+      <c r="E32" s="3">
         <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M33" t="s">
+        <v>58</v>
+      </c>
+      <c r="N33" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M34" t="s">
+        <v>59</v>
+      </c>
+      <c r="N34" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M35" t="s">
+        <v>62</v>
+      </c>
+      <c r="N35" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/LubanConfig/MiniTemplate/Datas/基础数据/#经济系统配置表.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/基础数据/#经济系统配置表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="82">
   <si>
     <t>每日商店</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -205,10 +205,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>计算一下纯靠通关，不看广告的话，获得的资源最多能打到哪里</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>获得次数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -221,10 +217,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>比例都是总需求-固定值的剩余的比例</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>注意：平均每次开精致宝箱的收益要高于普通宝箱</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -249,31 +241,135 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10次广告，每个广告获得500金币。 剩余的5000金币，分配给两个钻石购买的礼包： 1000金币  100钻石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>工作1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>工作2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>金币每日固定数值，要加入购买次数的考虑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>金币和钻石的价值分配，要考虑到  广告获得金币的占比</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>工作3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>考虑每日商店的购买次数，以及每种碎片的钻石定价</t>
+    <t>计算每日不看广告只通关的情况下，最多的关卡进度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算通关奖励最少奖励和宝箱最少奖励，一起并入每日固定产出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绿色的定价为1钻石，</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>在程序里写了，10次广告，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>每个广告获得500金币</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>。 剩余的5000金币，分配给两个钻石购买的礼包： 1000金币  100钻石</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现价金币和钻石兑换比是1:10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工作4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工作5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工作6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>保底绿色碎片</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>保底蓝色碎片</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>保底紫色碎片</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>保底</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>保底金币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>保底钻石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每个类型为“比例”的数值，都有一个“保底”类型的数值，用于限制它的最小值。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>考虑保底钻石对每日钻石需求的影响</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>保底资源，都是 保底 两个字+ 资源名的格式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工作7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据每天的产出，分配到每关的产出奖励</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算精致宝箱升级，和每级的产出资源数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工作8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>按养成强度来计算关卡数值，替代角色平均等级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>保底资源的价值要能达到200钻石的成本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>精致宝箱保底价值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通宝箱保底价值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>比例   是 总需求-固定值的剩余的比例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果价值比变了，保底价值要重新计算</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -281,7 +377,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -303,6 +399,31 @@
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -359,16 +480,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -649,12 +773,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S35"/>
+  <dimension ref="A1:S56"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
     <col min="2" max="2" width="14.875" style="3" customWidth="1"/>
-    <col min="3" max="6" width="9" style="3"/>
+    <col min="3" max="3" width="21" style="3" customWidth="1"/>
+    <col min="4" max="6" width="9" style="3"/>
+    <col min="12" max="12" width="26.75" customWidth="1"/>
     <col min="13" max="13" width="23.75" customWidth="1"/>
   </cols>
   <sheetData>
@@ -665,12 +791,12 @@
       <c r="B1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
       <c r="G1" s="1" t="s">
         <v>41</v>
       </c>
@@ -678,7 +804,7 @@
         <v>43</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -688,12 +814,12 @@
       <c r="B2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
       <c r="G2" s="1" t="s">
         <v>42</v>
       </c>
@@ -701,7 +827,7 @@
         <v>42</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -746,17 +872,29 @@
       <c r="B5" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="5">
         <v>10</v>
       </c>
+      <c r="G5" s="9">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
       <c r="M5" t="s">
-        <v>56</v>
+        <v>54</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.2">
@@ -772,14 +910,8 @@
       <c r="F6" s="3">
         <v>5</v>
       </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
       <c r="M6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
@@ -795,14 +927,8 @@
       <c r="F7" s="3">
         <v>5</v>
       </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
       <c r="M7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
@@ -818,14 +944,8 @@
       <c r="F8" s="3">
         <v>4</v>
       </c>
-      <c r="H8">
-        <v>2</v>
-      </c>
-      <c r="I8">
-        <v>2</v>
-      </c>
       <c r="M8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.2">
@@ -861,210 +981,210 @@
       <c r="E10" s="3">
         <v>0.1</v>
       </c>
+      <c r="M10" s="7" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="3">
+        <v>10</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="C12" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" s="3">
+        <v>5</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C13" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E13" s="5">
         <v>1</v>
       </c>
-      <c r="G11">
+      <c r="G13">
         <v>200</v>
       </c>
-      <c r="H11">
+      <c r="H13">
         <v>8</v>
       </c>
-      <c r="I11">
+      <c r="I13">
         <v>9</v>
       </c>
-      <c r="Q11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="C12" s="5" t="s">
+      <c r="Q13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="C14" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E14" s="4">
         <v>100</v>
-      </c>
-      <c r="I12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="C13" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="3">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="C14" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="S14" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E15" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="M15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="C16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="S16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="C17" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="3">
         <v>0.7</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B16" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="6">
-        <v>10</v>
-      </c>
-      <c r="G16">
-        <v>500</v>
-      </c>
-      <c r="H16">
-        <v>1</v>
-      </c>
-      <c r="M16" t="s">
-        <v>44</v>
-      </c>
-      <c r="N16" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="5">
-        <v>10000</v>
-      </c>
-      <c r="M17" t="s">
-        <v>57</v>
-      </c>
-    </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B18" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" s="5">
-        <v>0.5</v>
+      <c r="C18" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" s="3">
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C19" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="2">
-        <v>0.5</v>
+      <c r="C19" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E19" s="3">
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C20" s="3" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="5">
+        <v>10</v>
+      </c>
+      <c r="G21">
+        <v>500</v>
+      </c>
+      <c r="M21" t="s">
+        <v>44</v>
+      </c>
+      <c r="N21" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="C22" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="4">
+        <v>10000</v>
+      </c>
+      <c r="M22" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B23" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="3">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="M21" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="3" t="s">
+      <c r="E23" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="M23" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="C24" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E23" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B24" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E24" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="M24" t="s">
-        <v>50</v>
+      <c r="E24" s="2">
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -1075,10 +1195,7 @@
         <v>9</v>
       </c>
       <c r="E25" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>32</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
@@ -1089,131 +1206,321 @@
         <v>9</v>
       </c>
       <c r="E26" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="C27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="C28" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E28" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="C29" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E29" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="C30" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E30" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="C31" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E31" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="C32" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E32" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="C33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B34" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="M34" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="C35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" s="3">
         <v>0.1</v>
       </c>
-      <c r="M26" t="s">
+      <c r="M35" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="C36" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="M36" t="s">
         <v>28</v>
       </c>
-      <c r="N26">
+      <c r="N36">
         <f>SUMIFS(E:E, C:C, "*蓝色碎片*", D:D, "*比例*")</f>
         <v>0.99999999999999989</v>
       </c>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="2" t="s">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="C37" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D37" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E37" s="2">
         <v>100</v>
       </c>
-      <c r="M27" t="s">
+      <c r="M37" t="s">
         <v>29</v>
       </c>
-      <c r="N27">
+      <c r="N37">
         <f>SUMIFS(E:E, C:C, "*绿色碎片*", D:D, "*比例*")</f>
         <v>0.99999999999999989</v>
       </c>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C28" s="3" t="s">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="C38" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D38" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E28" s="3">
+      <c r="E38" s="3">
         <v>10</v>
       </c>
-      <c r="M28" t="s">
+      <c r="M38" t="s">
         <v>30</v>
       </c>
-      <c r="N28">
+      <c r="N38">
         <f>SUMIFS(E:E, C:C, "*紫色碎片*", D:D, "*比例*")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B29" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="2">
-        <v>50</v>
-      </c>
-      <c r="M29" t="s">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="C39" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E39" s="3">
+        <v>100</v>
+      </c>
+      <c r="M39" t="s">
         <v>31</v>
       </c>
-      <c r="N29">
+      <c r="N39">
         <f>SUMIFS(E:E, C:C, "*金币*", D:D, "*比例*")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B30" s="3" t="s">
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="C40" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E40" s="3">
+        <v>5</v>
+      </c>
+      <c r="M40" t="s">
+        <v>78</v>
+      </c>
+      <c r="N40">
+        <f>E18*1+E19*3+E20*10+10</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="C41" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3</v>
+      </c>
+      <c r="M41" t="s">
+        <v>79</v>
+      </c>
+      <c r="N41">
+        <f>E11*1+E12*3</f>
+        <v>25</v>
+      </c>
+      <c r="P41" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B43" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C43" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D43" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E43" s="4">
         <v>500</v>
       </c>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="2" t="s">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="C44" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E31" s="2">
+      <c r="E44" s="2">
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C32" s="3" t="s">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="C45" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E45" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M33" t="s">
-        <v>58</v>
-      </c>
-      <c r="N33" t="s">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="M48" t="s">
+        <v>60</v>
+      </c>
+      <c r="N48" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="49" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="N49" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="50" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M50" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="34" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M34" t="s">
-        <v>59</v>
-      </c>
-      <c r="N34" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="35" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M35" t="s">
+      <c r="N50" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="51" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M51" t="s">
         <v>62</v>
       </c>
-      <c r="N35" t="s">
-        <v>63</v>
+      <c r="N51" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="53" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M53" t="s">
+        <v>72</v>
+      </c>
+      <c r="N53" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="56" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M56" t="s">
+        <v>75</v>
+      </c>
+      <c r="N56" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/LubanConfig/MiniTemplate/Datas/基础数据/#经济系统配置表.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/基础数据/#经济系统配置表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="85">
   <si>
     <t>每日商店</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -242,10 +242,6 @@
   </si>
   <si>
     <t>计算每日不看广告只通关的情况下，最多的关卡进度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计算通关奖励最少奖励和宝箱最少奖励，一起并入每日固定产出</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -285,14 +281,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>工作4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>工作5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>工作6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -325,10 +313,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>考虑保底钻石对每日钻石需求的影响</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>保底资源，都是 保底 两个字+ 资源名的格式</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -370,6 +354,34 @@
   </si>
   <si>
     <t>如果价值比变了，保底价值要重新计算</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工作9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>理想情况下，开8次升一级，正好对应玩家每天开8次收益最大</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>但是实际上玩家不一定开8次，可能开10次。如果开10次就会</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宝箱的升级，应该按照每日产出里，角色的等级来。如果当天角色升级了，那么宝箱等级增加，如果没有升级，那么就不增加。没有升级的那几天，宝箱也不升级，那么那几天开宝箱都不会让宝箱升级，从而算出多少次开宝箱不升级，算出所需的钻石数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所以根据角色每天升级的规律来计算宝箱升级的规律。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数值问题：钻石价格太高，并且开的次数多，导致产出过多，产出总大于需求，宝箱就没有升级必要了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>要么提高整体碎片定价，要么减少钻石宝箱价格和开箱次数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -487,12 +499,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -773,7 +785,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S56"/>
+  <dimension ref="A1:S71"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -791,12 +803,12 @@
       <c r="B1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
       <c r="G1" s="1" t="s">
         <v>41</v>
       </c>
@@ -814,12 +826,12 @@
       <c r="B2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
       <c r="G2" s="1" t="s">
         <v>42</v>
       </c>
@@ -881,7 +893,7 @@
       <c r="E5" s="5">
         <v>10</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="8">
         <v>1</v>
       </c>
       <c r="H5">
@@ -893,8 +905,8 @@
       <c r="M5" t="s">
         <v>54</v>
       </c>
-      <c r="N5" s="8" t="s">
-        <v>57</v>
+      <c r="N5" s="7" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.2">
@@ -981,36 +993,36 @@
       <c r="E10" s="3">
         <v>0.1</v>
       </c>
-      <c r="M10" s="7" t="s">
-        <v>69</v>
+      <c r="M10" s="6" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="E11" s="3">
         <v>10</v>
       </c>
-      <c r="M11" s="7" t="s">
-        <v>71</v>
+      <c r="M11" s="6" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E12" s="3">
         <v>5</v>
       </c>
-      <c r="M12" s="7" t="s">
-        <v>77</v>
+      <c r="M12" s="6" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.2">
@@ -1091,10 +1103,10 @@
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="E18" s="3">
         <v>90</v>
@@ -1102,10 +1114,10 @@
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C19" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E19" s="3">
         <v>20</v>
@@ -1113,10 +1125,10 @@
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C20" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E20" s="3">
         <v>4</v>
@@ -1156,7 +1168,7 @@
         <v>10000</v>
       </c>
       <c r="M22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -1173,7 +1185,7 @@
         <v>0.5</v>
       </c>
       <c r="M23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.2">
@@ -1222,10 +1234,10 @@
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C28" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="E28" s="3">
         <v>10</v>
@@ -1233,10 +1245,10 @@
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C29" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E29" s="3">
         <v>5</v>
@@ -1244,10 +1256,10 @@
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C30" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E30" s="3">
         <v>1</v>
@@ -1255,10 +1267,10 @@
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C31" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E31" s="3">
         <v>100</v>
@@ -1266,10 +1278,10 @@
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C32" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E32" s="3">
         <v>10</v>
@@ -1300,7 +1312,7 @@
         <v>0.5</v>
       </c>
       <c r="M34" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" spans="2:16" x14ac:dyDescent="0.2">
@@ -1373,10 +1385,10 @@
     </row>
     <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E39" s="3">
         <v>100</v>
@@ -1391,16 +1403,16 @@
     </row>
     <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="E40" s="3">
         <v>5</v>
       </c>
       <c r="M40" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="N40">
         <f>E18*1+E19*3+E20*10+10</f>
@@ -1409,23 +1421,23 @@
     </row>
     <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E41" s="3">
         <v>3</v>
       </c>
       <c r="M41" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="N41">
         <f>E11*1+E12*3</f>
         <v>25</v>
       </c>
       <c r="P41" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42" spans="2:16" x14ac:dyDescent="0.2">
@@ -1478,49 +1490,66 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="M48" t="s">
-        <v>60</v>
-      </c>
-      <c r="N48" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="49" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="N49" t="s">
-        <v>70</v>
-      </c>
-    </row>
     <row r="50" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M50" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="N50" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M51" t="s">
-        <v>62</v>
-      </c>
       <c r="N51" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="52" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="N52" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="53" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="N53" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="54" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="N54" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="57" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M57" t="s">
+        <v>68</v>
+      </c>
+      <c r="N57" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="60" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M60" t="s">
+        <v>71</v>
+      </c>
+      <c r="N60" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="65" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M65" t="s">
+        <v>78</v>
+      </c>
+      <c r="N65" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="53" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M53" t="s">
-        <v>72</v>
-      </c>
-      <c r="N53" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="56" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M56" t="s">
-        <v>75</v>
-      </c>
-      <c r="N56" t="s">
-        <v>76</v>
+    <row r="70" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M70" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="71" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M71" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/LubanConfig/MiniTemplate/Datas/基础数据/#经济系统配置表.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/基础数据/#经济系统配置表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="73">
   <si>
     <t>每日商店</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -238,10 +238,6 @@
   </si>
   <si>
     <t>1广告位</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计算每日不看广告只通关的情况下，最多的关卡进度</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -281,10 +277,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>工作6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>保底绿色碎片</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -317,26 +309,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>工作7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>根据每天的产出，分配到每关的产出奖励</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计算精致宝箱升级，和每级的产出资源数量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>工作8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>按养成强度来计算关卡数值，替代角色平均等级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>保底资源的价值要能达到200钻石的成本</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -354,26 +326,6 @@
   </si>
   <si>
     <t>如果价值比变了，保底价值要重新计算</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>工作9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>理想情况下，开8次升一级，正好对应玩家每天开8次收益最大</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>但是实际上玩家不一定开8次，可能开10次。如果开10次就会</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>宝箱的升级，应该按照每日产出里，角色的等级来。如果当天角色升级了，那么宝箱等级增加，如果没有升级，那么就不增加。没有升级的那几天，宝箱也不升级，那么那几天开宝箱都不会让宝箱升级，从而算出多少次开宝箱不升级，算出所需的钻石数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>所以根据角色每天升级的规律来计算宝箱升级的规律。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -785,7 +737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S71"/>
+  <dimension ref="A1:S47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -906,7 +858,7 @@
         <v>54</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.2">
@@ -994,35 +946,35 @@
         <v>0.1</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E11" s="3">
         <v>10</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="E12" s="3">
         <v>5</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.2">
@@ -1103,10 +1055,10 @@
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C18" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E18" s="3">
         <v>90</v>
@@ -1114,10 +1066,10 @@
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C19" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="E19" s="3">
         <v>20</v>
@@ -1125,10 +1077,10 @@
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C20" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E20" s="3">
         <v>4</v>
@@ -1168,7 +1120,7 @@
         <v>10000</v>
       </c>
       <c r="M22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -1185,7 +1137,7 @@
         <v>0.5</v>
       </c>
       <c r="M23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.2">
@@ -1234,10 +1186,10 @@
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C28" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E28" s="3">
         <v>10</v>
@@ -1245,10 +1197,10 @@
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C29" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="E29" s="3">
         <v>5</v>
@@ -1256,10 +1208,10 @@
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C30" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E30" s="3">
         <v>1</v>
@@ -1267,10 +1219,10 @@
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C31" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E31" s="3">
         <v>100</v>
@@ -1278,10 +1230,10 @@
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C32" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E32" s="3">
         <v>10</v>
@@ -1312,7 +1264,7 @@
         <v>0.5</v>
       </c>
       <c r="M34" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="35" spans="2:16" x14ac:dyDescent="0.2">
@@ -1385,10 +1337,10 @@
     </row>
     <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E39" s="3">
         <v>100</v>
@@ -1403,16 +1355,16 @@
     </row>
     <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E40" s="3">
         <v>5</v>
       </c>
       <c r="M40" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="N40">
         <f>E18*1+E19*3+E20*10+10</f>
@@ -1421,23 +1373,23 @@
     </row>
     <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="E41" s="3">
         <v>3</v>
       </c>
       <c r="M41" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="N41">
         <f>E11*1+E12*3</f>
         <v>25</v>
       </c>
       <c r="P41" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="2:16" x14ac:dyDescent="0.2">
@@ -1490,66 +1442,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M50" t="s">
-        <v>59</v>
-      </c>
-      <c r="N50" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="51" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="N51" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="52" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="N52" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="53" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="N53" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="54" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="N54" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="57" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M57" t="s">
-        <v>68</v>
-      </c>
-      <c r="N57" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="60" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M60" t="s">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="M46" t="s">
         <v>71</v>
       </c>
-      <c r="N60" t="s">
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="M47" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="65" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M65" t="s">
-        <v>78</v>
-      </c>
-      <c r="N65" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="70" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M70" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="71" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M71" t="s">
-        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/LubanConfig/MiniTemplate/Datas/基础数据/#经济系统配置表.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/基础数据/#经济系统配置表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="74">
   <si>
     <t>每日商店</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -334,6 +334,10 @@
   </si>
   <si>
     <t>要么提高整体碎片定价，要么减少钻石宝箱价格和开箱次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通关产出中的保底数据是 每日的总计，不是单个</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1161,6 +1165,9 @@
       <c r="E25" s="3">
         <v>0.3</v>
       </c>
+      <c r="M25" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C26" s="3" t="s">

--- a/LubanConfig/MiniTemplate/Datas/基础数据/#经济系统配置表.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/基础数据/#经济系统配置表.xlsx
@@ -1199,7 +1199,7 @@
         <v>61</v>
       </c>
       <c r="E28" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.2">
@@ -1210,7 +1210,7 @@
         <v>61</v>
       </c>
       <c r="E29" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.2">
@@ -1221,7 +1221,7 @@
         <v>61</v>
       </c>
       <c r="E30" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">

--- a/LubanConfig/MiniTemplate/Datas/基础数据/#经济系统配置表.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/基础数据/#经济系统配置表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="75">
   <si>
     <t>每日商店</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -338,6 +338,10 @@
   </si>
   <si>
     <t>通关产出中的保底数据是 每日的总计，不是单个</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>500金币的数值如果修改，需要在totalsupply中修改</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1046,7 +1050,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C17" s="3" t="s">
         <v>6</v>
       </c>
@@ -1057,7 +1061,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C18" s="3" t="s">
         <v>58</v>
       </c>
@@ -1068,7 +1072,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C19" s="3" t="s">
         <v>59</v>
       </c>
@@ -1079,7 +1083,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C20" s="3" t="s">
         <v>60</v>
       </c>
@@ -1090,7 +1094,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
         <v>11</v>
       </c>
@@ -1113,7 +1117,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C22" s="4" t="s">
         <v>10</v>
       </c>
@@ -1127,7 +1131,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B23" s="3" t="s">
         <v>14</v>
       </c>
@@ -1143,8 +1147,11 @@
       <c r="M23" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O23" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C24" s="2" t="s">
         <v>3</v>
       </c>
@@ -1155,7 +1162,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C25" s="3" t="s">
         <v>5</v>
       </c>
@@ -1169,7 +1176,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C26" s="3" t="s">
         <v>7</v>
       </c>
@@ -1180,7 +1187,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C27" s="3" t="s">
         <v>6</v>
       </c>
@@ -1191,7 +1198,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C28" s="3" t="s">
         <v>58</v>
       </c>
@@ -1202,7 +1209,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C29" s="3" t="s">
         <v>59</v>
       </c>
@@ -1213,7 +1220,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C30" s="3" t="s">
         <v>60</v>
       </c>
@@ -1224,7 +1231,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C31" s="3" t="s">
         <v>62</v>
       </c>
@@ -1235,7 +1242,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C32" s="3" t="s">
         <v>63</v>
       </c>

--- a/LubanConfig/MiniTemplate/Datas/基础数据/#经济系统配置表.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/基础数据/#经济系统配置表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="89">
   <si>
     <t>每日商店</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -194,10 +194,6 @@
   </si>
   <si>
     <t>购买次数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一个500，一个2000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -273,10 +269,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>现价金币和钻石兑换比是1:10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>保底绿色碎片</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -297,10 +289,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>保底钻石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>每个类型为“比例”的数值，都有一个“保底”类型的数值，用于限制它的最小值。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -342,6 +330,74 @@
   </si>
   <si>
     <t>500金币的数值如果修改，需要在totalsupply中修改</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>平衡时价值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绿色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓝色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>紫色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>比例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>保底紫色碎片</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>保底</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现价金币和钻石兑换比是10:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要花费钻石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>钻石购买的金币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兑换比例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每个广告钻石价值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每个广告产出金币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拉平产出钻石的广告价值和产出金币的广告价值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>紫色碎片</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>固定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2是因为平均到每天是2，实际是第七天开出15个</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -349,7 +405,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -398,8 +454,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -421,6 +492,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,7 +529,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -462,6 +539,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -745,7 +825,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S47"/>
+  <dimension ref="A1:S49"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -763,12 +843,12 @@
       <c r="B1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
       <c r="G1" s="1" t="s">
         <v>41</v>
       </c>
@@ -776,7 +856,7 @@
         <v>43</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -786,12 +866,12 @@
       <c r="B2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
       <c r="G2" s="1" t="s">
         <v>42</v>
       </c>
@@ -799,7 +879,7 @@
         <v>42</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -854,7 +934,7 @@
         <v>10</v>
       </c>
       <c r="G5" s="8">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -863,10 +943,13 @@
         <v>1</v>
       </c>
       <c r="M5" t="s">
+        <v>53</v>
+      </c>
+      <c r="N5" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="N5" s="7" t="s">
-        <v>55</v>
+      <c r="P5" s="11">
+        <v>4.386574074074074E-2</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.2">
@@ -877,13 +960,13 @@
         <v>8</v>
       </c>
       <c r="E6" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F6" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
@@ -894,30 +977,30 @@
         <v>8</v>
       </c>
       <c r="E7" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F7" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="C8" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="10">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1</v>
+      </c>
+      <c r="M8" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="C8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="3">
-        <v>4</v>
-      </c>
-      <c r="F8" s="3">
-        <v>4</v>
-      </c>
-      <c r="M8" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.2">
@@ -934,7 +1017,7 @@
         <v>0.1</v>
       </c>
       <c r="G9">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H9">
         <v>4</v>
@@ -954,35 +1037,35 @@
         <v>0.1</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E11" s="3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="E12" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.2">
@@ -1008,7 +1091,7 @@
         <v>9</v>
       </c>
       <c r="Q13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.2">
@@ -1019,7 +1102,7 @@
         <v>8</v>
       </c>
       <c r="E14" s="4">
-        <v>100</v>
+        <v>500</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
@@ -1033,7 +1116,7 @@
         <v>0.5</v>
       </c>
       <c r="M15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
@@ -1047,54 +1130,54 @@
         <v>0.5</v>
       </c>
       <c r="S16" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="C17" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="C17" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="3">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="E17" s="10">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C18" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E18" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="C19" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="C20" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E18" s="3">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="C19" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E19" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="C20" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="E20" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
         <v>11</v>
       </c>
@@ -1108,16 +1191,13 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>500</v>
-      </c>
-      <c r="M21" t="s">
+        <v>600</v>
+      </c>
+      <c r="N21" t="s">
         <v>44</v>
       </c>
-      <c r="N21" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C22" s="4" t="s">
         <v>10</v>
       </c>
@@ -1128,10 +1208,10 @@
         <v>10000</v>
       </c>
       <c r="M22" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B23" s="3" t="s">
         <v>14</v>
       </c>
@@ -1142,16 +1222,16 @@
         <v>9</v>
       </c>
       <c r="E23" s="4">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="M23" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="O23" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C24" s="2" t="s">
         <v>3</v>
       </c>
@@ -1159,10 +1239,10 @@
         <v>8</v>
       </c>
       <c r="E24" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C25" s="3" t="s">
         <v>5</v>
       </c>
@@ -1170,13 +1250,13 @@
         <v>9</v>
       </c>
       <c r="E25" s="3">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="M25" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C26" s="3" t="s">
         <v>7</v>
       </c>
@@ -1184,136 +1264,172 @@
         <v>9</v>
       </c>
       <c r="E26" s="3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="C27" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="10">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>800</v>
+      </c>
+      <c r="N27" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="C28" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E28" s="3">
+        <v>15</v>
+      </c>
+      <c r="M28">
+        <v>600</v>
+      </c>
+      <c r="N28" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="C29" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" s="3">
+        <v>5</v>
+      </c>
+      <c r="M29">
+        <f>E22-M27*E21</f>
+        <v>2000</v>
+      </c>
+      <c r="N29" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="30" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="C30" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <f>M28/M29</f>
         <v>0.3</v>
       </c>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="C27" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E27" s="3">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="C28" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E28" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="C29" s="3" t="s">
+      <c r="N30" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="C31" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E29" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="C30" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E30" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="C31" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="E31" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="M31">
+        <f>M27*M30</f>
+        <v>240</v>
+      </c>
+      <c r="N31" t="s">
+        <v>83</v>
+      </c>
+      <c r="P31" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C32" s="3" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B33" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="C33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B34" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D34" s="4" t="s">
+      <c r="D33" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E34" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="M34" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="E33" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="M33" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="C34" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E35" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="M35" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="36" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="C36" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E36" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="M36" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="M35" t="s">
         <v>28</v>
       </c>
-      <c r="N36">
+      <c r="N35">
         <f>SUMIFS(E:E, C:C, "*蓝色碎片*", D:D, "*比例*")</f>
-        <v>0.99999999999999989</v>
-      </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="C36" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E36" s="10">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C37" s="2" t="s">
         <v>3</v>
       </c>
@@ -1321,17 +1437,26 @@
         <v>8</v>
       </c>
       <c r="E37" s="2">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M37" t="s">
         <v>29</v>
       </c>
       <c r="N37">
         <f>SUMIFS(E:E, C:C, "*绿色碎片*", D:D, "*比例*")</f>
-        <v>0.99999999999999989</v>
-      </c>
-    </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="P37" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>73</v>
+      </c>
+      <c r="R37">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="3" t="s">
         <v>24</v>
       </c>
@@ -1348,13 +1473,19 @@
         <f>SUMIFS(E:E, C:C, "*紫色碎片*", D:D, "*比例*")</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" t="s">
+        <v>74</v>
+      </c>
+      <c r="R38">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E39" s="3">
         <v>100</v>
@@ -1366,104 +1497,135 @@
         <f>SUMIFS(E:E, C:C, "*金币*", D:D, "*比例*")</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" t="s">
+        <v>75</v>
+      </c>
+      <c r="R39">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E40" s="3">
+        <v>15</v>
+      </c>
+      <c r="M40" t="s">
+        <v>64</v>
+      </c>
+      <c r="N40">
+        <f>E18*10+E19*30+E20*100+10</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="C41" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E41" s="3">
         <v>5</v>
       </c>
-      <c r="M40" t="s">
+      <c r="M41" t="s">
+        <v>65</v>
+      </c>
+      <c r="N41">
+        <f>E11*10+E12*30</f>
+        <v>50</v>
+      </c>
+      <c r="P41" t="s">
         <v>67</v>
       </c>
-      <c r="N40">
-        <f>E18*1+E19*3+E20*10+10</f>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="C42" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="C44" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E44" s="10">
+        <v>2</v>
+      </c>
+      <c r="M44" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="4">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="C46" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="2">
         <v>200</v>
       </c>
     </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="C41" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E41" s="3">
-        <v>3</v>
-      </c>
-      <c r="M41" t="s">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="C47" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="M48" t="s">
         <v>68</v>
       </c>
-      <c r="N41">
-        <f>E11*1+E12*3</f>
-        <v>25</v>
-      </c>
-      <c r="P41" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B43" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="4">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="C44" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E44" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="C45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="M46" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="M47" t="s">
-        <v>72</v>
+    </row>
+    <row r="49" spans="13:13" x14ac:dyDescent="0.2">
+      <c r="M49" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/LubanConfig/MiniTemplate/Datas/基础数据/#经济系统配置表.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/基础数据/#经济系统配置表.xlsx
@@ -241,6 +241,138 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>保底绿色碎片</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>保底蓝色碎片</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>保底紫色碎片</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>保底</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>保底金币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每个类型为“比例”的数值，都有一个“保底”类型的数值，用于限制它的最小值。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>保底资源，都是 保底 两个字+ 资源名的格式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>保底资源的价值要能达到200钻石的成本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>精致宝箱保底价值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通宝箱保底价值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>比例   是 总需求-固定值的剩余的比例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果价值比变了，保底价值要重新计算</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数值问题：钻石价格太高，并且开的次数多，导致产出过多，产出总大于需求，宝箱就没有升级必要了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>要么提高整体碎片定价，要么减少钻石宝箱价格和开箱次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通关产出中的保底数据是 每日的总计，不是单个</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>500金币的数值如果修改，需要在totalsupply中修改</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>平衡时价值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绿色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓝色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>紫色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>比例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>保底紫色碎片</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>保底</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现价金币和钻石兑换比是10:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要花费钻石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>钻石购买的金币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兑换比例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每个广告钻石价值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每个广告产出金币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拉平产出钻石的广告价值和产出金币的广告价值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>紫色碎片</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>固定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2是因为平均到每天是2，实际是第七天开出15个</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t>在程序里写了，10次广告，</t>
     </r>
@@ -254,7 +386,30 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>每个广告获得500金币</t>
+      <t>每个广告获得</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>800</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>金币</t>
     </r>
     <r>
       <rPr>
@@ -268,144 +423,12 @@
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
-  <si>
-    <t>保底绿色碎片</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>保底蓝色碎片</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>保底紫色碎片</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>保底</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>保底金币</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每个类型为“比例”的数值，都有一个“保底”类型的数值，用于限制它的最小值。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>保底资源，都是 保底 两个字+ 资源名的格式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>保底资源的价值要能达到200钻石的成本</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>精致宝箱保底价值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>普通宝箱保底价值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>比例   是 总需求-固定值的剩余的比例</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>如果价值比变了，保底价值要重新计算</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数值问题：钻石价格太高，并且开的次数多，导致产出过多，产出总大于需求，宝箱就没有升级必要了。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>要么提高整体碎片定价，要么减少钻石宝箱价格和开箱次数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>通关产出中的保底数据是 每日的总计，不是单个</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>500金币的数值如果修改，需要在totalsupply中修改</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>平衡时价值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>绿色</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>蓝色</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>紫色</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>比例</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>保底紫色碎片</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>保底</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>现价金币和钻石兑换比是10:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>需要花费钻石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>钻石购买的金币</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>兑换比例</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每个广告钻石价值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每个广告产出金币</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>拉平产出钻石的广告价值和产出金币的广告价值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>紫色碎片</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>固定</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2是因为平均到每天是2，实际是第七天开出15个</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -467,6 +490,14 @@
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1037,35 +1068,35 @@
         <v>0.1</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E11" s="3">
         <v>2</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E12" s="3">
         <v>1</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.2">
@@ -1102,7 +1133,7 @@
         <v>8</v>
       </c>
       <c r="E14" s="4">
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
@@ -1146,10 +1177,10 @@
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C18" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E18" s="3">
         <v>7</v>
@@ -1157,10 +1188,10 @@
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C19" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E19" s="3">
         <v>4</v>
@@ -1168,10 +1199,10 @@
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C20" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1208,7 +1239,7 @@
         <v>10000</v>
       </c>
       <c r="M22" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.2">
@@ -1225,10 +1256,10 @@
         <v>0.1</v>
       </c>
       <c r="M23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.2">
@@ -1253,7 +1284,7 @@
         <v>0.1</v>
       </c>
       <c r="M25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.2">
@@ -1281,15 +1312,15 @@
         <v>800</v>
       </c>
       <c r="N27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C28" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E28" s="3">
         <v>15</v>
@@ -1298,15 +1329,15 @@
         <v>600</v>
       </c>
       <c r="N28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C29" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E29" s="3">
         <v>5</v>
@@ -1316,15 +1347,15 @@
         <v>2000</v>
       </c>
       <c r="N29" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C30" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="E30" s="3">
         <v>0</v>
@@ -1334,15 +1365,15 @@
         <v>0.3</v>
       </c>
       <c r="N30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C31" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E31" s="3">
         <v>100</v>
@@ -1352,10 +1383,10 @@
         <v>240</v>
       </c>
       <c r="N31" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P31" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.2">
@@ -1383,7 +1414,7 @@
         <v>0.9</v>
       </c>
       <c r="M33" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.2">
@@ -1423,7 +1454,7 @@
         <v>6</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E36" s="10">
         <v>0.2</v>
@@ -1437,7 +1468,7 @@
         <v>8</v>
       </c>
       <c r="E37" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M37" t="s">
         <v>29</v>
@@ -1447,10 +1478,10 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q37" t="s">
         <v>72</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>73</v>
       </c>
       <c r="R37">
         <v>90</v>
@@ -1474,7 +1505,7 @@
         <v>1</v>
       </c>
       <c r="Q38" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="R38">
         <v>30</v>
@@ -1482,10 +1513,10 @@
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E39" s="3">
         <v>100</v>
@@ -1498,7 +1529,7 @@
         <v>1</v>
       </c>
       <c r="Q39" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R39">
         <v>4</v>
@@ -1506,16 +1537,16 @@
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E40" s="3">
         <v>15</v>
       </c>
       <c r="M40" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N40">
         <f>E18*10+E19*30+E20*100+10</f>
@@ -1524,31 +1555,31 @@
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E41" s="3">
         <v>5</v>
       </c>
       <c r="M41" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N41">
         <f>E11*10+E12*30</f>
         <v>50</v>
       </c>
       <c r="P41" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -1570,16 +1601,16 @@
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D44" s="10" t="s">
         <v>86</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>87</v>
       </c>
       <c r="E44" s="10">
         <v>2</v>
       </c>
       <c r="M44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.2">
@@ -1604,7 +1635,7 @@
         <v>8</v>
       </c>
       <c r="E46" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.2">
@@ -1620,12 +1651,12 @@
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="M48" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M49" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
